--- a/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
+++ b/data/CASTRO CALDERON VERONICA SOBEIDA.xlsx
@@ -446,9 +446,9 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -465,22 +465,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>septiembre</t>
+          <t>octubre</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
